--- a/documentacao/Testes/Caso de Teste/UC43 -  MANTER MEDICAMENTOS.xlsx
+++ b/documentacao/Testes/Caso de Teste/UC43 -  MANTER MEDICAMENTOS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t xml:space="preserve">Evidência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observações v2</t>
   </si>
   <si>
     <t xml:space="preserve">CT01</t>
@@ -278,7 +284,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -315,12 +321,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -380,7 +380,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -410,18 +410,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -608,8 +604,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="32.2578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="32.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.59"/>
@@ -640,301 +636,360 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="80.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="E7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="F15" s="8"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="F16" s="8"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
